--- a/Sindhi Muslim/Student Attendance/ECE (Deffodils)/ECE (Daffodils) Monthly Attendance - oCTOBER-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/ECE (Deffodils)/ECE (Daffodils) Monthly Attendance - oCTOBER-2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\ECE (Deffodils)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0506FAF-0116-4114-B245-3436A6333F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6615CBAA-5BE4-4A3F-9FE6-9B00A934C3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE (Daffodil) (Girls)" sheetId="17" r:id="rId1"/>
@@ -653,7 +653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -691,31 +691,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -746,18 +725,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -773,10 +740,31 @@
     <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="17" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -791,26 +779,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="38">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -859,6 +861,84 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -928,6 +1008,99 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1264,111 +1437,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
-      <c r="AH1" s="19"/>
-      <c r="AI1" s="19"/>
-      <c r="AJ1" s="19"/>
-      <c r="AK1" s="20"/>
-      <c r="AL1" s="20"/>
-      <c r="AM1" s="20"/>
-      <c r="AN1" s="20"/>
-      <c r="AO1" s="20"/>
-      <c r="AP1" s="20"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+      <c r="AA1" s="35"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
+      <c r="AF1" s="35"/>
+      <c r="AG1" s="35"/>
+      <c r="AH1" s="35"/>
+      <c r="AI1" s="35"/>
+      <c r="AJ1" s="35"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="21"/>
-      <c r="AJ2" s="21"/>
-      <c r="AK2" s="20"/>
-      <c r="AL2" s="20"/>
-      <c r="AM2" s="20"/>
-      <c r="AN2" s="20"/>
-      <c r="AO2" s="20"/>
-      <c r="AP2" s="20"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="16"/>
+      <c r="AL2" s="16"/>
+      <c r="AM2" s="16"/>
+      <c r="AN2" s="16"/>
+      <c r="AO2" s="16"/>
+      <c r="AP2" s="16"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="39" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1495,25 +1668,25 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="16" t="s">
+      <c r="AK3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="16" t="s">
+      <c r="AL3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="23" t="s">
+      <c r="AM3" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="23"/>
-      <c r="AO3" s="24"/>
-      <c r="AP3" s="24"/>
+      <c r="AN3" s="38"/>
+      <c r="AO3" s="17"/>
+      <c r="AP3" s="17"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="13">
         <v>45566</v>
       </c>
@@ -1607,16 +1780,16 @@
       <c r="AJ4" s="13">
         <v>45596</v>
       </c>
-      <c r="AK4" s="16"/>
-      <c r="AL4" s="16"/>
+      <c r="AK4" s="37"/>
+      <c r="AL4" s="37"/>
       <c r="AM4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="AN4" s="4">
         <v>31</v>
       </c>
-      <c r="AO4" s="24"/>
-      <c r="AP4" s="24"/>
+      <c r="AO4" s="17"/>
+      <c r="AP4" s="17"/>
     </row>
     <row r="5" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -1649,7 +1822,7 @@
       <c r="J5" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="40" t="s">
         <v>118</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -1670,7 +1843,7 @@
       <c r="Q5" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R5" s="17" t="s">
+      <c r="R5" s="40" t="s">
         <v>118</v>
       </c>
       <c r="S5" s="8" t="s">
@@ -1691,7 +1864,7 @@
       <c r="X5" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y5" s="17" t="s">
+      <c r="Y5" s="40" t="s">
         <v>118</v>
       </c>
       <c r="Z5" s="8" t="s">
@@ -1712,7 +1885,7 @@
       <c r="AE5" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF5" s="17" t="s">
+      <c r="AF5" s="51" t="s">
         <v>118</v>
       </c>
       <c r="AG5" s="8" t="s">
@@ -1741,10 +1914,10 @@
       <c r="AN5" s="9">
         <v>26</v>
       </c>
-      <c r="AO5" s="25" t="s">
+      <c r="AO5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="AP5" s="24"/>
+      <c r="AP5" s="17"/>
     </row>
     <row r="6" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
@@ -1777,7 +1950,7 @@
       <c r="J6" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K6" s="17"/>
+      <c r="K6" s="40"/>
       <c r="L6" s="8" t="s">
         <v>121</v>
       </c>
@@ -1796,7 +1969,7 @@
       <c r="Q6" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R6" s="17"/>
+      <c r="R6" s="40"/>
       <c r="S6" s="8" t="s">
         <v>121</v>
       </c>
@@ -1815,7 +1988,7 @@
       <c r="X6" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y6" s="17"/>
+      <c r="Y6" s="40"/>
       <c r="Z6" s="8" t="s">
         <v>121</v>
       </c>
@@ -1834,7 +2007,7 @@
       <c r="AE6" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AF6" s="17"/>
+      <c r="AF6" s="52"/>
       <c r="AG6" s="8" t="s">
         <v>121</v>
       </c>
@@ -1861,8 +2034,8 @@
       <c r="AN6" s="9">
         <v>4</v>
       </c>
-      <c r="AO6" s="24"/>
-      <c r="AP6" s="24"/>
+      <c r="AO6" s="17"/>
+      <c r="AP6" s="17"/>
     </row>
     <row r="7" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -1895,7 +2068,7 @@
       <c r="J7" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K7" s="17"/>
+      <c r="K7" s="40"/>
       <c r="L7" s="8" t="s">
         <v>121</v>
       </c>
@@ -1914,7 +2087,7 @@
       <c r="Q7" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R7" s="17"/>
+      <c r="R7" s="40"/>
       <c r="S7" s="8" t="s">
         <v>121</v>
       </c>
@@ -1933,7 +2106,7 @@
       <c r="X7" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="Y7" s="17"/>
+      <c r="Y7" s="40"/>
       <c r="Z7" s="8" t="s">
         <v>122</v>
       </c>
@@ -1952,7 +2125,7 @@
       <c r="AE7" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AF7" s="17"/>
+      <c r="AF7" s="52"/>
       <c r="AG7" s="8" t="s">
         <v>121</v>
       </c>
@@ -1973,10 +2146,10 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="AM7" s="24"/>
-      <c r="AN7" s="24"/>
-      <c r="AO7" s="24"/>
-      <c r="AP7" s="24"/>
+      <c r="AM7" s="17"/>
+      <c r="AN7" s="17"/>
+      <c r="AO7" s="17"/>
+      <c r="AP7" s="17"/>
     </row>
     <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -2009,7 +2182,7 @@
       <c r="J8" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K8" s="17"/>
+      <c r="K8" s="40"/>
       <c r="L8" s="8" t="s">
         <v>121</v>
       </c>
@@ -2028,7 +2201,7 @@
       <c r="Q8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R8" s="17"/>
+      <c r="R8" s="40"/>
       <c r="S8" s="8" t="s">
         <v>122</v>
       </c>
@@ -2047,7 +2220,7 @@
       <c r="X8" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y8" s="17"/>
+      <c r="Y8" s="40"/>
       <c r="Z8" s="8" t="s">
         <v>121</v>
       </c>
@@ -2066,7 +2239,7 @@
       <c r="AE8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AF8" s="17"/>
+      <c r="AF8" s="52"/>
       <c r="AG8" s="8" t="s">
         <v>121</v>
       </c>
@@ -2087,12 +2260,12 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="AM8" s="23" t="s">
+      <c r="AM8" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="AN8" s="23"/>
-      <c r="AO8" s="23"/>
-      <c r="AP8" s="23"/>
+      <c r="AN8" s="38"/>
+      <c r="AO8" s="38"/>
+      <c r="AP8" s="38"/>
     </row>
     <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -2125,7 +2298,7 @@
       <c r="J9" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="17"/>
+      <c r="K9" s="40"/>
       <c r="L9" s="8" t="s">
         <v>122</v>
       </c>
@@ -2144,7 +2317,7 @@
       <c r="Q9" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="R9" s="17"/>
+      <c r="R9" s="40"/>
       <c r="S9" s="8" t="s">
         <v>123</v>
       </c>
@@ -2163,7 +2336,7 @@
       <c r="X9" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="Y9" s="17"/>
+      <c r="Y9" s="40"/>
       <c r="Z9" s="8" t="s">
         <v>123</v>
       </c>
@@ -2182,7 +2355,7 @@
       <c r="AE9" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="AF9" s="17"/>
+      <c r="AF9" s="52"/>
       <c r="AG9" s="8" t="s">
         <v>123</v>
       </c>
@@ -2247,7 +2420,7 @@
       <c r="J10" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K10" s="17"/>
+      <c r="K10" s="40"/>
       <c r="L10" s="8" t="s">
         <v>121</v>
       </c>
@@ -2266,7 +2439,7 @@
       <c r="Q10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R10" s="17"/>
+      <c r="R10" s="40"/>
       <c r="S10" s="8" t="s">
         <v>121</v>
       </c>
@@ -2285,7 +2458,7 @@
       <c r="X10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y10" s="17"/>
+      <c r="Y10" s="40"/>
       <c r="Z10" s="8" t="s">
         <v>121</v>
       </c>
@@ -2304,7 +2477,7 @@
       <c r="AE10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF10" s="17"/>
+      <c r="AF10" s="52"/>
       <c r="AG10" s="8" t="s">
         <v>121</v>
       </c>
@@ -2372,7 +2545,7 @@
       <c r="J11" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K11" s="17"/>
+      <c r="K11" s="40"/>
       <c r="L11" s="8" t="s">
         <v>121</v>
       </c>
@@ -2391,7 +2564,7 @@
       <c r="Q11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R11" s="17"/>
+      <c r="R11" s="40"/>
       <c r="S11" s="8" t="s">
         <v>121</v>
       </c>
@@ -2410,7 +2583,7 @@
       <c r="X11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y11" s="17"/>
+      <c r="Y11" s="40"/>
       <c r="Z11" s="8" t="s">
         <v>121</v>
       </c>
@@ -2429,7 +2602,7 @@
       <c r="AE11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF11" s="17"/>
+      <c r="AF11" s="52"/>
       <c r="AG11" s="8" t="s">
         <v>121</v>
       </c>
@@ -2497,7 +2670,7 @@
       <c r="J12" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K12" s="17"/>
+      <c r="K12" s="40"/>
       <c r="L12" s="8" t="s">
         <v>122</v>
       </c>
@@ -2516,7 +2689,7 @@
       <c r="Q12" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R12" s="17"/>
+      <c r="R12" s="40"/>
       <c r="S12" s="8" t="s">
         <v>121</v>
       </c>
@@ -2535,7 +2708,7 @@
       <c r="X12" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y12" s="17"/>
+      <c r="Y12" s="40"/>
       <c r="Z12" s="8" t="s">
         <v>121</v>
       </c>
@@ -2554,7 +2727,7 @@
       <c r="AE12" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF12" s="17"/>
+      <c r="AF12" s="52"/>
       <c r="AG12" s="8" t="s">
         <v>121</v>
       </c>
@@ -2622,7 +2795,7 @@
       <c r="J13" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K13" s="17"/>
+      <c r="K13" s="40"/>
       <c r="L13" s="8" t="s">
         <v>121</v>
       </c>
@@ -2641,7 +2814,7 @@
       <c r="Q13" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R13" s="17"/>
+      <c r="R13" s="40"/>
       <c r="S13" s="8" t="s">
         <v>121</v>
       </c>
@@ -2660,7 +2833,7 @@
       <c r="X13" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y13" s="17"/>
+      <c r="Y13" s="40"/>
       <c r="Z13" s="8" t="s">
         <v>121</v>
       </c>
@@ -2679,7 +2852,7 @@
       <c r="AE13" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF13" s="17"/>
+      <c r="AF13" s="52"/>
       <c r="AG13" s="8" t="s">
         <v>121</v>
       </c>
@@ -2700,10 +2873,10 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AM13" s="24"/>
-      <c r="AN13" s="26"/>
-      <c r="AO13" s="26"/>
-      <c r="AP13" s="26"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="19"/>
     </row>
     <row r="14" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
@@ -2736,7 +2909,7 @@
       <c r="J14" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K14" s="17"/>
+      <c r="K14" s="40"/>
       <c r="L14" s="8" t="s">
         <v>121</v>
       </c>
@@ -2755,7 +2928,7 @@
       <c r="Q14" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R14" s="17"/>
+      <c r="R14" s="40"/>
       <c r="S14" s="8" t="s">
         <v>121</v>
       </c>
@@ -2774,7 +2947,7 @@
       <c r="X14" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y14" s="17"/>
+      <c r="Y14" s="40"/>
       <c r="Z14" s="8" t="s">
         <v>121</v>
       </c>
@@ -2793,7 +2966,7 @@
       <c r="AE14" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AF14" s="17"/>
+      <c r="AF14" s="52"/>
       <c r="AG14" s="8" t="s">
         <v>122</v>
       </c>
@@ -2814,10 +2987,10 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="AM14" s="27"/>
-      <c r="AN14" s="27"/>
-      <c r="AO14" s="27"/>
-      <c r="AP14" s="27"/>
+      <c r="AM14" s="20"/>
+      <c r="AN14" s="20"/>
+      <c r="AO14" s="20"/>
+      <c r="AP14" s="20"/>
     </row>
     <row r="15" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
@@ -2850,7 +3023,7 @@
       <c r="J15" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K15" s="17"/>
+      <c r="K15" s="40"/>
       <c r="L15" s="8" t="s">
         <v>121</v>
       </c>
@@ -2869,7 +3042,7 @@
       <c r="Q15" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R15" s="17"/>
+      <c r="R15" s="40"/>
       <c r="S15" s="8" t="s">
         <v>122</v>
       </c>
@@ -2888,7 +3061,7 @@
       <c r="X15" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y15" s="17"/>
+      <c r="Y15" s="40"/>
       <c r="Z15" s="8" t="s">
         <v>121</v>
       </c>
@@ -2907,7 +3080,7 @@
       <c r="AE15" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF15" s="17"/>
+      <c r="AF15" s="52"/>
       <c r="AG15" s="8" t="s">
         <v>121</v>
       </c>
@@ -2928,10 +3101,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AM15" s="24"/>
-      <c r="AN15" s="24"/>
-      <c r="AO15" s="24"/>
-      <c r="AP15" s="24"/>
+      <c r="AM15" s="17"/>
+      <c r="AN15" s="17"/>
+      <c r="AO15" s="17"/>
+      <c r="AP15" s="17"/>
     </row>
     <row r="16" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
@@ -2964,7 +3137,7 @@
       <c r="J16" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K16" s="17"/>
+      <c r="K16" s="40"/>
       <c r="L16" s="8" t="s">
         <v>121</v>
       </c>
@@ -2983,7 +3156,7 @@
       <c r="Q16" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R16" s="17"/>
+      <c r="R16" s="40"/>
       <c r="S16" s="8" t="s">
         <v>121</v>
       </c>
@@ -3002,7 +3175,7 @@
       <c r="X16" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y16" s="17"/>
+      <c r="Y16" s="40"/>
       <c r="Z16" s="8" t="s">
         <v>121</v>
       </c>
@@ -3021,7 +3194,7 @@
       <c r="AE16" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF16" s="17"/>
+      <c r="AF16" s="52"/>
       <c r="AG16" s="8" t="s">
         <v>121</v>
       </c>
@@ -3042,12 +3215,12 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AM16" s="23" t="s">
+      <c r="AM16" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="23"/>
-      <c r="AO16" s="23"/>
-      <c r="AP16" s="23"/>
+      <c r="AN16" s="38"/>
+      <c r="AO16" s="38"/>
+      <c r="AP16" s="38"/>
     </row>
     <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -3080,7 +3253,7 @@
       <c r="J17" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K17" s="17"/>
+      <c r="K17" s="40"/>
       <c r="L17" s="8" t="s">
         <v>121</v>
       </c>
@@ -3099,7 +3272,7 @@
       <c r="Q17" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="R17" s="17"/>
+      <c r="R17" s="40"/>
       <c r="S17" s="8" t="s">
         <v>123</v>
       </c>
@@ -3118,7 +3291,7 @@
       <c r="X17" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y17" s="17"/>
+      <c r="Y17" s="40"/>
       <c r="Z17" s="8" t="s">
         <v>121</v>
       </c>
@@ -3137,7 +3310,7 @@
       <c r="AE17" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF17" s="17"/>
+      <c r="AF17" s="52"/>
       <c r="AG17" s="8" t="s">
         <v>121</v>
       </c>
@@ -3202,7 +3375,7 @@
       <c r="J18" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K18" s="17"/>
+      <c r="K18" s="40"/>
       <c r="L18" s="8" t="s">
         <v>121</v>
       </c>
@@ -3221,7 +3394,7 @@
       <c r="Q18" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R18" s="17"/>
+      <c r="R18" s="40"/>
       <c r="S18" s="8" t="s">
         <v>122</v>
       </c>
@@ -3240,7 +3413,7 @@
       <c r="X18" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y18" s="17"/>
+      <c r="Y18" s="40"/>
       <c r="Z18" s="8" t="s">
         <v>122</v>
       </c>
@@ -3259,7 +3432,7 @@
       <c r="AE18" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AF18" s="17"/>
+      <c r="AF18" s="52"/>
       <c r="AG18" s="8" t="s">
         <v>121</v>
       </c>
@@ -3327,7 +3500,7 @@
       <c r="J19" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K19" s="17"/>
+      <c r="K19" s="40"/>
       <c r="L19" s="8" t="s">
         <v>121</v>
       </c>
@@ -3346,7 +3519,7 @@
       <c r="Q19" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R19" s="17"/>
+      <c r="R19" s="40"/>
       <c r="S19" s="8" t="s">
         <v>122</v>
       </c>
@@ -3365,7 +3538,7 @@
       <c r="X19" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y19" s="17"/>
+      <c r="Y19" s="40"/>
       <c r="Z19" s="8" t="s">
         <v>121</v>
       </c>
@@ -3384,7 +3557,7 @@
       <c r="AE19" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF19" s="17"/>
+      <c r="AF19" s="52"/>
       <c r="AG19" s="8" t="s">
         <v>121</v>
       </c>
@@ -3452,7 +3625,7 @@
       <c r="J20" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K20" s="17"/>
+      <c r="K20" s="40"/>
       <c r="L20" s="8" t="s">
         <v>121</v>
       </c>
@@ -3471,7 +3644,7 @@
       <c r="Q20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R20" s="17"/>
+      <c r="R20" s="40"/>
       <c r="S20" s="8" t="s">
         <v>121</v>
       </c>
@@ -3490,7 +3663,7 @@
       <c r="X20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y20" s="17"/>
+      <c r="Y20" s="40"/>
       <c r="Z20" s="8" t="s">
         <v>121</v>
       </c>
@@ -3509,7 +3682,7 @@
       <c r="AE20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF20" s="17"/>
+      <c r="AF20" s="52"/>
       <c r="AG20" s="8" t="s">
         <v>121</v>
       </c>
@@ -3577,7 +3750,7 @@
       <c r="J21" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K21" s="17"/>
+      <c r="K21" s="40"/>
       <c r="L21" s="8" t="s">
         <v>121</v>
       </c>
@@ -3596,7 +3769,7 @@
       <c r="Q21" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R21" s="17"/>
+      <c r="R21" s="40"/>
       <c r="S21" s="8" t="s">
         <v>121</v>
       </c>
@@ -3615,7 +3788,7 @@
       <c r="X21" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y21" s="17"/>
+      <c r="Y21" s="40"/>
       <c r="Z21" s="8" t="s">
         <v>121</v>
       </c>
@@ -3634,7 +3807,7 @@
       <c r="AE21" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF21" s="17"/>
+      <c r="AF21" s="52"/>
       <c r="AG21" s="8" t="s">
         <v>121</v>
       </c>
@@ -3655,10 +3828,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AM21" s="20"/>
-      <c r="AN21" s="20"/>
-      <c r="AO21" s="20"/>
-      <c r="AP21" s="20"/>
+      <c r="AM21" s="16"/>
+      <c r="AN21" s="16"/>
+      <c r="AO21" s="16"/>
+      <c r="AP21" s="16"/>
     </row>
     <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
@@ -3691,7 +3864,7 @@
       <c r="J22" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K22" s="17"/>
+      <c r="K22" s="40"/>
       <c r="L22" s="8" t="s">
         <v>121</v>
       </c>
@@ -3710,7 +3883,7 @@
       <c r="Q22" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R22" s="17"/>
+      <c r="R22" s="40"/>
       <c r="S22" s="8" t="s">
         <v>121</v>
       </c>
@@ -3729,7 +3902,7 @@
       <c r="X22" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y22" s="17"/>
+      <c r="Y22" s="40"/>
       <c r="Z22" s="8" t="s">
         <v>121</v>
       </c>
@@ -3748,7 +3921,7 @@
       <c r="AE22" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF22" s="17"/>
+      <c r="AF22" s="52"/>
       <c r="AG22" s="8" t="s">
         <v>122</v>
       </c>
@@ -3769,10 +3942,10 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="AM22" s="20"/>
-      <c r="AN22" s="20"/>
-      <c r="AO22" s="20"/>
-      <c r="AP22" s="20"/>
+      <c r="AM22" s="16"/>
+      <c r="AN22" s="16"/>
+      <c r="AO22" s="16"/>
+      <c r="AP22" s="16"/>
     </row>
     <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
@@ -3805,7 +3978,7 @@
       <c r="J23" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K23" s="17"/>
+      <c r="K23" s="40"/>
       <c r="L23" s="8" t="s">
         <v>122</v>
       </c>
@@ -3824,7 +3997,7 @@
       <c r="Q23" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R23" s="17"/>
+      <c r="R23" s="40"/>
       <c r="S23" s="8" t="s">
         <v>122</v>
       </c>
@@ -3843,7 +4016,7 @@
       <c r="X23" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="Y23" s="17"/>
+      <c r="Y23" s="40"/>
       <c r="Z23" s="8" t="s">
         <v>121</v>
       </c>
@@ -3862,7 +4035,7 @@
       <c r="AE23" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF23" s="17"/>
+      <c r="AF23" s="52"/>
       <c r="AG23" s="8" t="s">
         <v>121</v>
       </c>
@@ -3883,10 +4056,10 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="AM23" s="20"/>
-      <c r="AN23" s="20"/>
-      <c r="AO23" s="20"/>
-      <c r="AP23" s="20"/>
+      <c r="AM23" s="16"/>
+      <c r="AN23" s="16"/>
+      <c r="AO23" s="16"/>
+      <c r="AP23" s="16"/>
     </row>
     <row r="24" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
@@ -3919,7 +4092,7 @@
       <c r="J24" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K24" s="17"/>
+      <c r="K24" s="40"/>
       <c r="L24" s="8" t="s">
         <v>121</v>
       </c>
@@ -3938,7 +4111,7 @@
       <c r="Q24" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R24" s="17"/>
+      <c r="R24" s="40"/>
       <c r="S24" s="8" t="s">
         <v>121</v>
       </c>
@@ -3957,7 +4130,7 @@
       <c r="X24" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y24" s="17"/>
+      <c r="Y24" s="40"/>
       <c r="Z24" s="8" t="s">
         <v>121</v>
       </c>
@@ -3976,7 +4149,7 @@
       <c r="AE24" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AF24" s="17"/>
+      <c r="AF24" s="52"/>
       <c r="AG24" s="8" t="s">
         <v>121</v>
       </c>
@@ -3997,10 +4170,10 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AM24" s="20"/>
-      <c r="AN24" s="20"/>
-      <c r="AO24" s="20"/>
-      <c r="AP24" s="20"/>
+      <c r="AM24" s="16"/>
+      <c r="AN24" s="16"/>
+      <c r="AO24" s="16"/>
+      <c r="AP24" s="16"/>
     </row>
     <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
@@ -4033,7 +4206,7 @@
       <c r="J25" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K25" s="17"/>
+      <c r="K25" s="40"/>
       <c r="L25" s="8" t="s">
         <v>121</v>
       </c>
@@ -4052,7 +4225,7 @@
       <c r="Q25" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R25" s="17"/>
+      <c r="R25" s="40"/>
       <c r="S25" s="8" t="s">
         <v>121</v>
       </c>
@@ -4071,7 +4244,7 @@
       <c r="X25" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y25" s="17"/>
+      <c r="Y25" s="40"/>
       <c r="Z25" s="8" t="s">
         <v>121</v>
       </c>
@@ -4090,7 +4263,7 @@
       <c r="AE25" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF25" s="17"/>
+      <c r="AF25" s="52"/>
       <c r="AG25" s="8" t="s">
         <v>121</v>
       </c>
@@ -4111,10 +4284,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AM25" s="20"/>
-      <c r="AN25" s="20"/>
-      <c r="AO25" s="20"/>
-      <c r="AP25" s="20"/>
+      <c r="AM25" s="16"/>
+      <c r="AN25" s="16"/>
+      <c r="AO25" s="16"/>
+      <c r="AP25" s="16"/>
     </row>
     <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
@@ -4147,7 +4320,7 @@
       <c r="J26" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K26" s="17"/>
+      <c r="K26" s="40"/>
       <c r="L26" s="8" t="s">
         <v>121</v>
       </c>
@@ -4166,7 +4339,7 @@
       <c r="Q26" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R26" s="17"/>
+      <c r="R26" s="40"/>
       <c r="S26" s="8" t="s">
         <v>121</v>
       </c>
@@ -4185,7 +4358,7 @@
       <c r="X26" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y26" s="17"/>
+      <c r="Y26" s="40"/>
       <c r="Z26" s="8" t="s">
         <v>121</v>
       </c>
@@ -4204,7 +4377,7 @@
       <c r="AE26" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF26" s="17"/>
+      <c r="AF26" s="52"/>
       <c r="AG26" s="8" t="s">
         <v>121</v>
       </c>
@@ -4225,10 +4398,10 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AM26" s="20"/>
-      <c r="AN26" s="20"/>
-      <c r="AO26" s="20"/>
-      <c r="AP26" s="20"/>
+      <c r="AM26" s="16"/>
+      <c r="AN26" s="16"/>
+      <c r="AO26" s="16"/>
+      <c r="AP26" s="16"/>
     </row>
     <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
@@ -4261,7 +4434,7 @@
       <c r="J27" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K27" s="17"/>
+      <c r="K27" s="40"/>
       <c r="L27" s="8" t="s">
         <v>122</v>
       </c>
@@ -4280,7 +4453,7 @@
       <c r="Q27" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R27" s="17"/>
+      <c r="R27" s="40"/>
       <c r="S27" s="8" t="s">
         <v>123</v>
       </c>
@@ -4299,7 +4472,7 @@
       <c r="X27" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="Y27" s="17"/>
+      <c r="Y27" s="40"/>
       <c r="Z27" s="8" t="s">
         <v>123</v>
       </c>
@@ -4318,7 +4491,7 @@
       <c r="AE27" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="AF27" s="17"/>
+      <c r="AF27" s="52"/>
       <c r="AG27" s="8" t="s">
         <v>123</v>
       </c>
@@ -4339,10 +4512,10 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="AM27" s="20"/>
-      <c r="AN27" s="20"/>
-      <c r="AO27" s="20"/>
-      <c r="AP27" s="20"/>
+      <c r="AM27" s="16"/>
+      <c r="AN27" s="16"/>
+      <c r="AO27" s="16"/>
+      <c r="AP27" s="16"/>
     </row>
     <row r="28" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
@@ -4375,7 +4548,7 @@
       <c r="J28" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="K28" s="17"/>
+      <c r="K28" s="40"/>
       <c r="L28" s="8" t="s">
         <v>121</v>
       </c>
@@ -4394,7 +4567,7 @@
       <c r="Q28" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="R28" s="17"/>
+      <c r="R28" s="40"/>
       <c r="S28" s="8" t="s">
         <v>122</v>
       </c>
@@ -4413,7 +4586,7 @@
       <c r="X28" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="Y28" s="17"/>
+      <c r="Y28" s="40"/>
       <c r="Z28" s="8" t="s">
         <v>123</v>
       </c>
@@ -4432,7 +4605,7 @@
       <c r="AE28" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AF28" s="17"/>
+      <c r="AF28" s="52"/>
       <c r="AG28" s="8" t="s">
         <v>121</v>
       </c>
@@ -4453,10 +4626,10 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="AM28" s="20"/>
-      <c r="AN28" s="20"/>
-      <c r="AO28" s="20"/>
-      <c r="AP28" s="20"/>
+      <c r="AM28" s="16"/>
+      <c r="AN28" s="16"/>
+      <c r="AO28" s="16"/>
+      <c r="AP28" s="16"/>
     </row>
     <row r="29" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
@@ -4485,7 +4658,7 @@
       <c r="J29" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="K29" s="17"/>
+      <c r="K29" s="40"/>
       <c r="L29" s="8" t="s">
         <v>121</v>
       </c>
@@ -4504,7 +4677,7 @@
       <c r="Q29" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="R29" s="17"/>
+      <c r="R29" s="40"/>
       <c r="S29" s="8" t="s">
         <v>121</v>
       </c>
@@ -4523,7 +4696,7 @@
       <c r="X29" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="Y29" s="17"/>
+      <c r="Y29" s="40"/>
       <c r="Z29" s="8" t="s">
         <v>121</v>
       </c>
@@ -4542,7 +4715,7 @@
       <c r="AE29" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AF29" s="20"/>
+      <c r="AF29" s="53"/>
       <c r="AG29" s="8" t="s">
         <v>121</v>
       </c>
@@ -4563,13 +4736,19 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="AM29" s="20"/>
-      <c r="AN29" s="20"/>
-      <c r="AO29" s="20"/>
-      <c r="AP29" s="20"/>
+      <c r="AM29" s="16"/>
+      <c r="AN29" s="16"/>
+      <c r="AO29" s="16"/>
+      <c r="AP29" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="AM8:AP8"/>
+    <mergeCell ref="AM16:AP16"/>
+    <mergeCell ref="K5:K29"/>
+    <mergeCell ref="R5:R29"/>
+    <mergeCell ref="Y5:Y29"/>
+    <mergeCell ref="AF5:AF29"/>
     <mergeCell ref="A1:AJ1"/>
     <mergeCell ref="A2:AJ2"/>
     <mergeCell ref="AK3:AK4"/>
@@ -4580,62 +4759,61 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="AM8:AP8"/>
-    <mergeCell ref="AM16:AP16"/>
-    <mergeCell ref="AF5:AF28"/>
-    <mergeCell ref="K5:K29"/>
-    <mergeCell ref="R5:R29"/>
-    <mergeCell ref="Y5:Y29"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B29">
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:J29 L6:Q29 S6:X29 Z6:AE29 F4:AJ5 AG6:AJ29">
-    <cfRule type="expression" dxfId="16" priority="9">
+  <conditionalFormatting sqref="F3:AJ5 F6:J29 L6:Q29 S6:X29 Z6:AE29 AG6:AJ29 AM4:AN4">
+    <cfRule type="expression" dxfId="36" priority="11">
+      <formula>F$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:AJ5 F6:J29 L6:Q29 S6:X29 Z6:AE29 AG6:AJ29">
+    <cfRule type="expression" dxfId="35" priority="10">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:J29 L6:Q29 S6:X29 Z6:AE29 F5:AJ5 AG6:AJ29">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+  <conditionalFormatting sqref="F5:AJ5 F6:J29 L6:Q29 S6:X29 Z6:AE29 AG6:AJ29">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM4:AN4 F6:J29 L6:Q29 S6:X29 Z6:AE29 F3:AJ5 AG6:AJ29">
-    <cfRule type="expression" dxfId="13" priority="10">
-      <formula>F$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AL3 AK5:AL29">
-    <cfRule type="expression" dxfId="12" priority="11">
+    <cfRule type="expression" dxfId="32" priority="12">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM6">
-    <cfRule type="expression" dxfId="11" priority="8">
+    <cfRule type="expression" dxfId="31" priority="9">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AM12">
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="30" priority="7">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AM20">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="29" priority="6">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN9:AP9">
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="28" priority="8">
       <formula>AN$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN17:AP17">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="27" priority="5">
       <formula>AN$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:AJ5 F6:AE29 AG6:AJ29">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+      <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4692,111 +4870,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AP1" s="18"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
+      <c r="AB1" s="48"/>
+      <c r="AC1" s="48"/>
+      <c r="AD1" s="48"/>
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="48"/>
+      <c r="AG1" s="48"/>
+      <c r="AH1" s="48"/>
+      <c r="AI1" s="48"/>
+      <c r="AJ1" s="48"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
-      <c r="AN2" s="18"/>
-      <c r="AO2" s="18"/>
-      <c r="AP2" s="18"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="47"/>
+      <c r="AC2" s="47"/>
+      <c r="AD2" s="47"/>
+      <c r="AE2" s="47"/>
+      <c r="AF2" s="47"/>
+      <c r="AG2" s="47"/>
+      <c r="AH2" s="47"/>
+      <c r="AI2" s="47"/>
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
+      <c r="AO2" s="15"/>
+      <c r="AP2" s="15"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="49" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -4923,122 +5101,122 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="38" t="s">
+      <c r="AK3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="38" t="s">
+      <c r="AL3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="18"/>
-      <c r="AN3" s="18"/>
-      <c r="AO3" s="18"/>
-      <c r="AP3" s="18"/>
+      <c r="AM3" s="15"/>
+      <c r="AN3" s="15"/>
+      <c r="AO3" s="15"/>
+      <c r="AP3" s="15"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40">
+      <c r="A4" s="50"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="29">
         <v>45566</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="29">
         <v>45567</v>
       </c>
-      <c r="H4" s="40">
+      <c r="H4" s="29">
         <v>45568</v>
       </c>
-      <c r="I4" s="40">
+      <c r="I4" s="29">
         <v>45569</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4" s="29">
         <v>45570</v>
       </c>
-      <c r="K4" s="40">
+      <c r="K4" s="29">
         <v>45571</v>
       </c>
-      <c r="L4" s="40">
+      <c r="L4" s="29">
         <v>45572</v>
       </c>
-      <c r="M4" s="40">
+      <c r="M4" s="29">
         <v>45573</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="29">
         <v>45574</v>
       </c>
-      <c r="O4" s="40">
+      <c r="O4" s="29">
         <v>45575</v>
       </c>
-      <c r="P4" s="40">
+      <c r="P4" s="29">
         <v>45576</v>
       </c>
-      <c r="Q4" s="40">
+      <c r="Q4" s="29">
         <v>45577</v>
       </c>
-      <c r="R4" s="40">
+      <c r="R4" s="29">
         <v>45578</v>
       </c>
-      <c r="S4" s="40">
+      <c r="S4" s="29">
         <v>45579</v>
       </c>
-      <c r="T4" s="40">
+      <c r="T4" s="29">
         <v>45580</v>
       </c>
-      <c r="U4" s="40">
+      <c r="U4" s="29">
         <v>45581</v>
       </c>
-      <c r="V4" s="40">
+      <c r="V4" s="29">
         <v>45582</v>
       </c>
-      <c r="W4" s="40">
+      <c r="W4" s="29">
         <v>45583</v>
       </c>
-      <c r="X4" s="40">
+      <c r="X4" s="29">
         <v>45584</v>
       </c>
-      <c r="Y4" s="40">
+      <c r="Y4" s="29">
         <v>45585</v>
       </c>
-      <c r="Z4" s="40">
+      <c r="Z4" s="29">
         <v>45586</v>
       </c>
-      <c r="AA4" s="40">
+      <c r="AA4" s="29">
         <v>45587</v>
       </c>
-      <c r="AB4" s="40">
+      <c r="AB4" s="29">
         <v>45588</v>
       </c>
-      <c r="AC4" s="40">
+      <c r="AC4" s="29">
         <v>45589</v>
       </c>
-      <c r="AD4" s="40">
+      <c r="AD4" s="29">
         <v>45590</v>
       </c>
-      <c r="AE4" s="40">
+      <c r="AE4" s="29">
         <v>45591</v>
       </c>
-      <c r="AF4" s="40">
+      <c r="AF4" s="29">
         <v>45592</v>
       </c>
-      <c r="AG4" s="40">
+      <c r="AG4" s="29">
         <v>45593</v>
       </c>
-      <c r="AH4" s="40">
+      <c r="AH4" s="29">
         <v>45594</v>
       </c>
-      <c r="AI4" s="40">
+      <c r="AI4" s="29">
         <v>45595</v>
       </c>
-      <c r="AJ4" s="40">
+      <c r="AJ4" s="29">
         <v>45596</v>
       </c>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="18"/>
-      <c r="AN4" s="18"/>
-      <c r="AO4" s="18"/>
-      <c r="AP4" s="18"/>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="41"/>
+      <c r="AM4" s="15"/>
+      <c r="AN4" s="15"/>
+      <c r="AO4" s="15"/>
+      <c r="AP4" s="15"/>
     </row>
     <row r="5" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
@@ -5047,106 +5225,106 @@
       <c r="B5" s="5">
         <v>61</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="42" t="s">
+      <c r="F5" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="J5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K5" s="48" t="s">
+      <c r="J5" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="L5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R5" s="48" t="s">
+      <c r="L5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R5" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="S5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y5" s="48" t="s">
+      <c r="S5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y5" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="Z5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF5" s="48" t="s">
+      <c r="Z5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF5" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="AG5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI5" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ5" s="30" t="s">
+      <c r="AG5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI5" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ5" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK5" s="3">
@@ -5157,10 +5335,10 @@
         <f t="shared" ref="AL5:AL35" si="2">COUNTIF(F5:AJ5,"A")</f>
         <v>2</v>
       </c>
-      <c r="AM5" s="18"/>
-      <c r="AN5" s="18"/>
-      <c r="AO5" s="18"/>
-      <c r="AP5" s="18"/>
+      <c r="AM5" s="15"/>
+      <c r="AN5" s="15"/>
+      <c r="AO5" s="15"/>
+      <c r="AP5" s="15"/>
     </row>
     <row r="6" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
@@ -5169,98 +5347,98 @@
       <c r="B6" s="10">
         <v>79</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="H6" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="I6" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="J6" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K6" s="49"/>
-      <c r="L6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R6" s="49"/>
-      <c r="S6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF6" s="49"/>
-      <c r="AG6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI6" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ6" s="30" t="s">
+      <c r="F6" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K6" s="45"/>
+      <c r="L6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R6" s="45"/>
+      <c r="S6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y6" s="45"/>
+      <c r="Z6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF6" s="45"/>
+      <c r="AG6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ6" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK6" s="3">
@@ -5271,12 +5449,12 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AM6" s="43" t="s">
+      <c r="AM6" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AN6" s="44"/>
-      <c r="AO6" s="33"/>
-      <c r="AP6" s="33"/>
+      <c r="AN6" s="43"/>
+      <c r="AO6" s="26"/>
+      <c r="AP6" s="26"/>
     </row>
     <row r="7" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
@@ -5285,98 +5463,98 @@
       <c r="B7" s="10">
         <v>16</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I7" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J7" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K7" s="49"/>
-      <c r="L7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R7" s="49"/>
-      <c r="S7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF7" s="49"/>
-      <c r="AG7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI7" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ7" s="30" t="s">
+      <c r="F7" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K7" s="45"/>
+      <c r="L7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R7" s="45"/>
+      <c r="S7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y7" s="45"/>
+      <c r="Z7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF7" s="45"/>
+      <c r="AG7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI7" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ7" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK7" s="3">
@@ -5393,8 +5571,8 @@
       <c r="AN7" s="3">
         <v>31</v>
       </c>
-      <c r="AO7" s="33"/>
-      <c r="AP7" s="33"/>
+      <c r="AO7" s="26"/>
+      <c r="AP7" s="26"/>
     </row>
     <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
@@ -5403,98 +5581,98 @@
       <c r="B8" s="10">
         <v>78</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G8" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H8" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I8" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J8" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K8" s="49"/>
-      <c r="L8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q8" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R8" s="49"/>
-      <c r="S8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W8" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="X8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y8" s="49"/>
-      <c r="Z8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF8" s="49"/>
-      <c r="AG8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI8" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ8" s="30" t="s">
+      <c r="F8" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K8" s="45"/>
+      <c r="L8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R8" s="45"/>
+      <c r="S8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="X8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y8" s="45"/>
+      <c r="Z8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF8" s="45"/>
+      <c r="AG8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ8" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK8" s="3">
@@ -5511,10 +5689,10 @@
       <c r="AN8" s="10">
         <v>26</v>
       </c>
-      <c r="AO8" s="33" t="s">
+      <c r="AO8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="AP8" s="33"/>
+      <c r="AP8" s="26"/>
     </row>
     <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
@@ -5523,98 +5701,98 @@
       <c r="B9" s="10">
         <v>76</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I9" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K9" s="49"/>
-      <c r="L9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R9" s="49"/>
-      <c r="S9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF9" s="49"/>
-      <c r="AG9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI9" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ9" s="30" t="s">
+      <c r="F9" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K9" s="45"/>
+      <c r="L9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R9" s="45"/>
+      <c r="S9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ9" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK9" s="3">
@@ -5631,8 +5809,8 @@
       <c r="AN9" s="10">
         <v>4</v>
       </c>
-      <c r="AO9" s="33"/>
-      <c r="AP9" s="33"/>
+      <c r="AO9" s="26"/>
+      <c r="AP9" s="26"/>
     </row>
     <row r="10" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
@@ -5641,98 +5819,98 @@
       <c r="B10" s="10">
         <v>95</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G10" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H10" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I10" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J10" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K10" s="49"/>
-      <c r="L10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P10" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q10" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R10" s="49"/>
-      <c r="S10" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="T10" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="U10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X10" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y10" s="49"/>
-      <c r="Z10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF10" s="49"/>
-      <c r="AG10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI10" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ10" s="30" t="s">
+      <c r="F10" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K10" s="45"/>
+      <c r="L10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P10" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q10" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R10" s="45"/>
+      <c r="S10" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="U10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X10" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y10" s="45"/>
+      <c r="Z10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF10" s="45"/>
+      <c r="AG10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ10" s="23" t="s">
         <v>122</v>
       </c>
       <c r="AK10" s="3">
@@ -5743,10 +5921,10 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="AM10" s="33"/>
-      <c r="AN10" s="33"/>
-      <c r="AO10" s="33"/>
-      <c r="AP10" s="33"/>
+      <c r="AM10" s="26"/>
+      <c r="AN10" s="26"/>
+      <c r="AO10" s="26"/>
+      <c r="AP10" s="26"/>
     </row>
     <row r="11" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
@@ -5755,98 +5933,98 @@
       <c r="B11" s="10">
         <v>96</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J11" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K11" s="49"/>
-      <c r="L11" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="M11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R11" s="49"/>
-      <c r="S11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V11" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="W11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD11" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE11" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF11" s="49"/>
-      <c r="AG11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI11" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ11" s="30" t="s">
+      <c r="F11" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K11" s="45"/>
+      <c r="L11" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R11" s="45"/>
+      <c r="S11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V11" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="W11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y11" s="45"/>
+      <c r="Z11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD11" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE11" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF11" s="45"/>
+      <c r="AG11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI11" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ11" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK11" s="3">
@@ -5857,12 +6035,12 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AM11" s="45" t="s">
+      <c r="AM11" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="AN11" s="46"/>
-      <c r="AO11" s="46"/>
-      <c r="AP11" s="47"/>
+      <c r="AN11" s="34"/>
+      <c r="AO11" s="34"/>
+      <c r="AP11" s="33"/>
     </row>
     <row r="12" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
@@ -5871,98 +6049,98 @@
       <c r="B12" s="10">
         <v>108</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H12" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I12" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K12" s="49"/>
-      <c r="L12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M12" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="N12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q12" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R12" s="49"/>
-      <c r="S12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X12" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD12" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE12" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF12" s="49"/>
-      <c r="AG12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI12" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ12" s="30" t="s">
+      <c r="F12" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" s="45"/>
+      <c r="L12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="N12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q12" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R12" s="45"/>
+      <c r="S12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X12" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y12" s="45"/>
+      <c r="Z12" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD12" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE12" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI12" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ12" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK12" s="3">
@@ -5996,98 +6174,98 @@
       <c r="B13" s="10">
         <v>131</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H13" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K13" s="49"/>
-      <c r="L13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P13" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R13" s="49"/>
-      <c r="S13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W13" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="X13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB13" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD13" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF13" s="49"/>
-      <c r="AG13" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH13" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI13" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ13" s="30" t="s">
+      <c r="F13" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K13" s="45"/>
+      <c r="L13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P13" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R13" s="45"/>
+      <c r="S13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W13" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="X13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y13" s="45"/>
+      <c r="Z13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB13" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD13" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF13" s="45"/>
+      <c r="AG13" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH13" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI13" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ13" s="23" t="s">
         <v>122</v>
       </c>
       <c r="AK13" s="3">
@@ -6121,98 +6299,98 @@
       <c r="B14" s="10">
         <v>101</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" s="49"/>
-      <c r="L14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R14" s="49"/>
-      <c r="S14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y14" s="49"/>
-      <c r="Z14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF14" s="49"/>
-      <c r="AG14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI14" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ14" s="30" t="s">
+      <c r="F14" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" s="45"/>
+      <c r="L14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R14" s="45"/>
+      <c r="S14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y14" s="45"/>
+      <c r="Z14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF14" s="45"/>
+      <c r="AG14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ14" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK14" s="3">
@@ -6246,98 +6424,98 @@
       <c r="B15" s="10">
         <v>100</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H15" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I15" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J15" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K15" s="49"/>
-      <c r="L15" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="M15" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="N15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R15" s="49"/>
-      <c r="S15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA15" s="30" t="s">
+      <c r="F15" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K15" s="45"/>
+      <c r="L15" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R15" s="45"/>
+      <c r="S15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y15" s="45"/>
+      <c r="Z15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA15" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AB15" s="30" t="s">
+      <c r="AB15" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AC15" s="30" t="s">
+      <c r="AC15" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AD15" s="30" t="s">
+      <c r="AD15" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AE15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF15" s="49"/>
-      <c r="AG15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI15" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ15" s="30" t="s">
+      <c r="AE15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF15" s="45"/>
+      <c r="AG15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI15" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ15" s="23" t="s">
         <v>122</v>
       </c>
       <c r="AK15" s="3">
@@ -6348,10 +6526,10 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AM15" s="33"/>
-      <c r="AN15" s="34"/>
-      <c r="AO15" s="34"/>
-      <c r="AP15" s="34"/>
+      <c r="AM15" s="26"/>
+      <c r="AN15" s="27"/>
+      <c r="AO15" s="27"/>
+      <c r="AP15" s="27"/>
     </row>
     <row r="16" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
@@ -6360,98 +6538,98 @@
       <c r="B16" s="10">
         <v>90</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G16" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H16" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J16" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K16" s="49"/>
-      <c r="L16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R16" s="49"/>
-      <c r="S16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y16" s="49"/>
-      <c r="Z16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF16" s="49"/>
-      <c r="AG16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI16" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ16" s="30" t="s">
+      <c r="F16" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K16" s="45"/>
+      <c r="L16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="45"/>
+      <c r="S16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y16" s="45"/>
+      <c r="Z16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF16" s="45"/>
+      <c r="AG16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI16" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ16" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK16" s="3">
@@ -6462,10 +6640,10 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="35"/>
-      <c r="AN16" s="35"/>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="35"/>
+      <c r="AM16" s="28"/>
+      <c r="AN16" s="28"/>
+      <c r="AO16" s="28"/>
+      <c r="AP16" s="28"/>
     </row>
     <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
@@ -6474,98 +6652,98 @@
       <c r="B17" s="10">
         <v>73</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J17" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R17" s="49"/>
-      <c r="S17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V17" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="W17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y17" s="49"/>
-      <c r="Z17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF17" s="49"/>
-      <c r="AG17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI17" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ17" s="30" t="s">
+      <c r="F17" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17" s="45"/>
+      <c r="L17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R17" s="45"/>
+      <c r="S17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V17" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="W17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y17" s="45"/>
+      <c r="Z17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF17" s="45"/>
+      <c r="AG17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ17" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK17" s="3">
@@ -6576,10 +6754,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AM17" s="33"/>
-      <c r="AN17" s="33"/>
-      <c r="AO17" s="33"/>
-      <c r="AP17" s="33"/>
+      <c r="AM17" s="26"/>
+      <c r="AN17" s="26"/>
+      <c r="AO17" s="26"/>
+      <c r="AP17" s="26"/>
     </row>
     <row r="18" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
@@ -6588,98 +6766,98 @@
       <c r="B18" s="10">
         <v>74</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H18" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="J18" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K18" s="49"/>
-      <c r="L18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R18" s="49"/>
-      <c r="S18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U18" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="V18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD18" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF18" s="49"/>
-      <c r="AG18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI18" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ18" s="30" t="s">
+      <c r="F18" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J18" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K18" s="45"/>
+      <c r="L18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R18" s="45"/>
+      <c r="S18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U18" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="V18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y18" s="45"/>
+      <c r="Z18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD18" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF18" s="45"/>
+      <c r="AG18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI18" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ18" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK18" s="3">
@@ -6710,98 +6888,98 @@
       <c r="B19" s="10">
         <v>77</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I19" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="J19" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K19" s="49"/>
-      <c r="L19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N19" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="O19" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="P19" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q19" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R19" s="49"/>
-      <c r="S19" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="T19" s="30" t="s">
+      <c r="F19" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J19" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" s="45"/>
+      <c r="L19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="O19" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="P19" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q19" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R19" s="45"/>
+      <c r="S19" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="T19" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="U19" s="30" t="s">
+      <c r="U19" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="V19" s="30" t="s">
+      <c r="V19" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="W19" s="30" t="s">
+      <c r="W19" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="X19" s="30" t="s">
+      <c r="X19" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="30" t="s">
+      <c r="Y19" s="45"/>
+      <c r="Z19" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AA19" s="30" t="s">
+      <c r="AA19" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AB19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF19" s="49"/>
-      <c r="AG19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ19" s="30" t="s">
+      <c r="AB19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF19" s="45"/>
+      <c r="AG19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI19" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ19" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK19" s="3">
@@ -6835,98 +7013,98 @@
       <c r="B20" s="10">
         <v>80</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="J20" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K20" s="49"/>
-      <c r="L20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q20" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R20" s="49"/>
-      <c r="S20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y20" s="49"/>
-      <c r="Z20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE20" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF20" s="49"/>
-      <c r="AG20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI20" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ20" s="30" t="s">
+      <c r="F20" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K20" s="45"/>
+      <c r="L20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q20" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R20" s="45"/>
+      <c r="S20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y20" s="45"/>
+      <c r="Z20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE20" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF20" s="45"/>
+      <c r="AG20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI20" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ20" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK20" s="3">
@@ -6960,98 +7138,98 @@
       <c r="B21" s="10">
         <v>93</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I21" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J21" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K21" s="49"/>
-      <c r="L21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R21" s="49"/>
-      <c r="S21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V21" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="W21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y21" s="49"/>
-      <c r="Z21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF21" s="49"/>
-      <c r="AG21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI21" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ21" s="30" t="s">
+      <c r="F21" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J21" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" s="45"/>
+      <c r="L21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R21" s="45"/>
+      <c r="S21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V21" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="W21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y21" s="45"/>
+      <c r="Z21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF21" s="45"/>
+      <c r="AG21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI21" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ21" s="23" t="s">
         <v>122</v>
       </c>
       <c r="AK21" s="3">
@@ -7062,10 +7240,10 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AM21" s="18"/>
-      <c r="AN21" s="18"/>
-      <c r="AO21" s="18"/>
-      <c r="AP21" s="18"/>
+      <c r="AM21" s="15"/>
+      <c r="AN21" s="15"/>
+      <c r="AO21" s="15"/>
+      <c r="AP21" s="15"/>
     </row>
     <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
@@ -7074,98 +7252,98 @@
       <c r="B22" s="10">
         <v>14</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G22" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H22" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J22" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K22" s="49"/>
-      <c r="L22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R22" s="49"/>
-      <c r="S22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="T22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="V22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="W22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="X22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y22" s="49"/>
-      <c r="Z22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF22" s="49"/>
-      <c r="AG22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH22" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI22" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ22" s="30" t="s">
+      <c r="F22" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I22" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J22" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K22" s="45"/>
+      <c r="L22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R22" s="45"/>
+      <c r="S22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="T22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="V22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="W22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="X22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y22" s="45"/>
+      <c r="Z22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF22" s="45"/>
+      <c r="AG22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH22" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ22" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK22" s="3">
@@ -7176,10 +7354,10 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="AM22" s="18"/>
-      <c r="AN22" s="18"/>
-      <c r="AO22" s="18"/>
-      <c r="AP22" s="18"/>
+      <c r="AM22" s="15"/>
+      <c r="AN22" s="15"/>
+      <c r="AO22" s="15"/>
+      <c r="AP22" s="15"/>
     </row>
     <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
@@ -7188,98 +7366,98 @@
       <c r="B23" s="10">
         <v>94</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G23" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H23" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J23" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K23" s="49"/>
-      <c r="L23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q23" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R23" s="49"/>
-      <c r="S23" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="T23" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="U23" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="V23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y23" s="49"/>
-      <c r="Z23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF23" s="49"/>
-      <c r="AG23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI23" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ23" s="30" t="s">
+      <c r="F23" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I23" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J23" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K23" s="45"/>
+      <c r="L23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q23" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R23" s="45"/>
+      <c r="S23" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="T23" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="U23" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="V23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y23" s="45"/>
+      <c r="Z23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF23" s="45"/>
+      <c r="AG23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI23" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ23" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK23" s="3">
@@ -7290,10 +7468,10 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AM23" s="18"/>
-      <c r="AN23" s="18"/>
-      <c r="AO23" s="18"/>
-      <c r="AP23" s="18"/>
+      <c r="AM23" s="15"/>
+      <c r="AN23" s="15"/>
+      <c r="AO23" s="15"/>
+      <c r="AP23" s="15"/>
     </row>
     <row r="24" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
@@ -7302,98 +7480,98 @@
       <c r="B24" s="10">
         <v>111</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G24" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J24" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K24" s="49"/>
-      <c r="L24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R24" s="49"/>
-      <c r="S24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y24" s="49"/>
-      <c r="Z24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF24" s="49"/>
-      <c r="AG24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI24" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ24" s="30" t="s">
+      <c r="F24" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J24" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K24" s="45"/>
+      <c r="L24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R24" s="45"/>
+      <c r="S24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y24" s="45"/>
+      <c r="Z24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF24" s="45"/>
+      <c r="AG24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI24" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ24" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK24" s="3">
@@ -7404,10 +7582,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AM24" s="18"/>
-      <c r="AN24" s="18"/>
-      <c r="AO24" s="18"/>
-      <c r="AP24" s="18"/>
+      <c r="AM24" s="15"/>
+      <c r="AN24" s="15"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
     </row>
     <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
@@ -7416,98 +7594,98 @@
       <c r="B25" s="10">
         <v>113</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="E25" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G25" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H25" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I25" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="J25" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K25" s="49"/>
-      <c r="L25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R25" s="49"/>
-      <c r="S25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y25" s="49"/>
-      <c r="Z25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF25" s="49"/>
-      <c r="AG25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI25" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ25" s="30" t="s">
+      <c r="F25" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J25" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K25" s="45"/>
+      <c r="L25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R25" s="45"/>
+      <c r="S25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y25" s="45"/>
+      <c r="Z25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF25" s="45"/>
+      <c r="AG25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ25" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK25" s="3">
@@ -7518,10 +7696,10 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AM25" s="18"/>
-      <c r="AN25" s="18"/>
-      <c r="AO25" s="18"/>
-      <c r="AP25" s="18"/>
+      <c r="AM25" s="15"/>
+      <c r="AN25" s="15"/>
+      <c r="AO25" s="15"/>
+      <c r="AP25" s="15"/>
     </row>
     <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
@@ -7530,98 +7708,98 @@
       <c r="B26" s="10">
         <v>115</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H26" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I26" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J26" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K26" s="49"/>
-      <c r="L26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R26" s="49"/>
-      <c r="S26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y26" s="49"/>
-      <c r="Z26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD26" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF26" s="49"/>
-      <c r="AG26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI26" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ26" s="30" t="s">
+      <c r="F26" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H26" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K26" s="45"/>
+      <c r="L26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R26" s="45"/>
+      <c r="S26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y26" s="45"/>
+      <c r="Z26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD26" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF26" s="45"/>
+      <c r="AG26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI26" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ26" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK26" s="3">
@@ -7632,10 +7810,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AM26" s="18"/>
-      <c r="AN26" s="18"/>
-      <c r="AO26" s="18"/>
-      <c r="AP26" s="18"/>
+      <c r="AM26" s="15"/>
+      <c r="AN26" s="15"/>
+      <c r="AO26" s="15"/>
+      <c r="AP26" s="15"/>
     </row>
     <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
@@ -7644,98 +7822,98 @@
       <c r="B27" s="10">
         <v>114</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H27" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I27" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J27" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K27" s="49"/>
-      <c r="L27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R27" s="49"/>
-      <c r="S27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD27" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF27" s="49"/>
-      <c r="AG27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI27" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ27" s="30" t="s">
+      <c r="F27" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J27" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K27" s="45"/>
+      <c r="L27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R27" s="45"/>
+      <c r="S27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y27" s="45"/>
+      <c r="Z27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD27" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF27" s="45"/>
+      <c r="AG27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI27" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ27" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK27" s="3">
@@ -7746,10 +7924,10 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AM27" s="18"/>
-      <c r="AN27" s="18"/>
-      <c r="AO27" s="18"/>
-      <c r="AP27" s="18"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
     </row>
     <row r="28" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
@@ -7758,98 +7936,98 @@
       <c r="B28" s="10">
         <v>141</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I28" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J28" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K28" s="49"/>
-      <c r="L28" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="M28" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="N28" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="O28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q28" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R28" s="49"/>
-      <c r="S28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X28" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y28" s="49"/>
-      <c r="Z28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE28" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF28" s="49"/>
-      <c r="AG28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI28" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ28" s="30" t="s">
+      <c r="F28" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H28" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J28" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K28" s="45"/>
+      <c r="L28" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="N28" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="O28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q28" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R28" s="45"/>
+      <c r="S28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X28" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y28" s="45"/>
+      <c r="Z28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE28" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF28" s="45"/>
+      <c r="AG28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI28" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ28" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK28" s="3">
@@ -7860,10 +8038,10 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="AM28" s="18"/>
-      <c r="AN28" s="18"/>
-      <c r="AO28" s="18"/>
-      <c r="AP28" s="18"/>
+      <c r="AM28" s="15"/>
+      <c r="AN28" s="15"/>
+      <c r="AO28" s="15"/>
+      <c r="AP28" s="15"/>
     </row>
     <row r="29" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
@@ -7872,98 +8050,98 @@
       <c r="B29" s="10">
         <v>140</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="30" t="s">
+      <c r="E29" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H29" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I29" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J29" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K29" s="49"/>
-      <c r="L29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q29" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R29" s="49"/>
-      <c r="S29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X29" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y29" s="49"/>
-      <c r="Z29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE29" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF29" s="49"/>
-      <c r="AG29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI29" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ29" s="30" t="s">
+      <c r="F29" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J29" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K29" s="45"/>
+      <c r="L29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q29" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R29" s="45"/>
+      <c r="S29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X29" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y29" s="45"/>
+      <c r="Z29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE29" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF29" s="45"/>
+      <c r="AG29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI29" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ29" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK29" s="3">
@@ -7974,106 +8152,106 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="AM29" s="18"/>
-      <c r="AN29" s="18"/>
-      <c r="AO29" s="18"/>
-      <c r="AP29" s="18"/>
+      <c r="AM29" s="15"/>
+      <c r="AN29" s="15"/>
+      <c r="AO29" s="15"/>
+      <c r="AP29" s="15"/>
     </row>
     <row r="30" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>26</v>
       </c>
       <c r="B30" s="10"/>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="30" t="s">
+      <c r="D30" s="25"/>
+      <c r="E30" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H30" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I30" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J30" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K30" s="49"/>
-      <c r="L30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P30" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q30" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R30" s="49"/>
-      <c r="S30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y30" s="49"/>
-      <c r="Z30" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF30" s="49"/>
-      <c r="AG30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI30" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ30" s="30" t="s">
+      <c r="F30" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I30" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J30" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K30" s="45"/>
+      <c r="L30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P30" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q30" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R30" s="45"/>
+      <c r="S30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y30" s="45"/>
+      <c r="Z30" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF30" s="45"/>
+      <c r="AG30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI30" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ30" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK30" s="3">
@@ -8084,108 +8262,108 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AM30" s="18"/>
-      <c r="AN30" s="18"/>
-      <c r="AO30" s="18"/>
-      <c r="AP30" s="18"/>
+      <c r="AM30" s="15"/>
+      <c r="AN30" s="15"/>
+      <c r="AO30" s="15"/>
+      <c r="AP30" s="15"/>
     </row>
     <row r="31" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>27</v>
       </c>
       <c r="B31" s="10"/>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="E31" s="30" t="s">
+      <c r="E31" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I31" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J31" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K31" s="49"/>
-      <c r="L31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q31" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R31" s="49"/>
-      <c r="S31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V31" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="W31" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="X31" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y31" s="49"/>
-      <c r="Z31" s="30" t="s">
+      <c r="F31" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J31" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K31" s="45"/>
+      <c r="L31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q31" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R31" s="45"/>
+      <c r="S31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V31" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="W31" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="X31" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y31" s="45"/>
+      <c r="Z31" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AA31" s="30" t="s">
+      <c r="AA31" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="AB31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF31" s="49"/>
-      <c r="AG31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH31" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI31" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ31" s="30" t="s">
+      <c r="AB31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF31" s="45"/>
+      <c r="AG31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH31" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI31" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ31" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK31" s="3">
@@ -8196,106 +8374,106 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="AM31" s="18"/>
-      <c r="AN31" s="18"/>
-      <c r="AO31" s="18"/>
-      <c r="AP31" s="18"/>
+      <c r="AM31" s="15"/>
+      <c r="AN31" s="15"/>
+      <c r="AO31" s="15"/>
+      <c r="AP31" s="15"/>
     </row>
     <row r="32" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>28</v>
       </c>
       <c r="B32" s="10"/>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="30" t="s">
+      <c r="D32" s="25"/>
+      <c r="E32" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G32" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H32" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I32" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J32" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K32" s="49"/>
-      <c r="L32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R32" s="49"/>
-      <c r="S32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y32" s="49"/>
-      <c r="Z32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD32" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="AE32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF32" s="49"/>
-      <c r="AG32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI32" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ32" s="30" t="s">
+      <c r="F32" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J32" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K32" s="45"/>
+      <c r="L32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R32" s="45"/>
+      <c r="S32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y32" s="45"/>
+      <c r="Z32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD32" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF32" s="45"/>
+      <c r="AG32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI32" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ32" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK32" s="3">
@@ -8306,10 +8484,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AM32" s="18"/>
-      <c r="AN32" s="18"/>
-      <c r="AO32" s="18"/>
-      <c r="AP32" s="18"/>
+      <c r="AM32" s="15"/>
+      <c r="AN32" s="15"/>
+      <c r="AO32" s="15"/>
+      <c r="AP32" s="15"/>
     </row>
     <row r="33" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
@@ -8318,98 +8496,98 @@
       <c r="B33" s="10">
         <v>72</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="E33" s="30" t="s">
+      <c r="E33" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H33" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I33" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J33" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K33" s="49"/>
-      <c r="L33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R33" s="49"/>
-      <c r="S33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y33" s="49"/>
-      <c r="Z33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF33" s="49"/>
-      <c r="AG33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI33" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ33" s="30" t="s">
+      <c r="F33" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I33" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J33" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K33" s="45"/>
+      <c r="L33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R33" s="45"/>
+      <c r="S33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y33" s="45"/>
+      <c r="Z33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF33" s="45"/>
+      <c r="AG33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI33" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ33" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK33" s="3">
@@ -8420,10 +8598,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AM33" s="18"/>
-      <c r="AN33" s="18"/>
-      <c r="AO33" s="18"/>
-      <c r="AP33" s="18"/>
+      <c r="AM33" s="15"/>
+      <c r="AN33" s="15"/>
+      <c r="AO33" s="15"/>
+      <c r="AP33" s="15"/>
     </row>
     <row r="34" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
@@ -8439,89 +8617,89 @@
         <v>103</v>
       </c>
       <c r="E34" s="10"/>
-      <c r="F34" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G34" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H34" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I34" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J34" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K34" s="49"/>
-      <c r="L34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="N34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="R34" s="49"/>
-      <c r="S34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X34" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y34" s="49"/>
-      <c r="Z34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF34" s="49"/>
-      <c r="AG34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI34" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ34" s="30" t="s">
+      <c r="F34" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H34" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I34" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J34" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K34" s="45"/>
+      <c r="L34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="N34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R34" s="45"/>
+      <c r="S34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X34" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y34" s="45"/>
+      <c r="Z34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF34" s="45"/>
+      <c r="AG34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI34" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ34" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK34" s="3">
@@ -8532,10 +8710,10 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AM34" s="18"/>
-      <c r="AN34" s="18"/>
-      <c r="AO34" s="18"/>
-      <c r="AP34" s="18"/>
+      <c r="AM34" s="15"/>
+      <c r="AN34" s="15"/>
+      <c r="AO34" s="15"/>
+      <c r="AP34" s="15"/>
     </row>
     <row r="35" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
@@ -8547,89 +8725,89 @@
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="H35" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I35" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="J35" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="K35" s="50"/>
-      <c r="L35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M35" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="N35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="O35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="P35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q35" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="R35" s="50"/>
-      <c r="S35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="T35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="U35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="V35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="W35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="X35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y35" s="50"/>
-      <c r="Z35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AD35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF35" s="50"/>
-      <c r="AG35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI35" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AJ35" s="30" t="s">
+      <c r="F35" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H35" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="I35" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="J35" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="K35" s="46"/>
+      <c r="L35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M35" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="N35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="O35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q35" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="R35" s="46"/>
+      <c r="S35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="T35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="U35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="V35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="W35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="X35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y35" s="46"/>
+      <c r="Z35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF35" s="46"/>
+      <c r="AG35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI35" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ35" s="23" t="s">
         <v>121</v>
       </c>
       <c r="AK35" s="3">
@@ -8640,18 +8818,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AM35" s="18"/>
-      <c r="AN35" s="18"/>
-      <c r="AO35" s="18"/>
-      <c r="AP35" s="18"/>
+      <c r="AM35" s="15"/>
+      <c r="AN35" s="15"/>
+      <c r="AO35" s="15"/>
+      <c r="AP35" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM6:AN6"/>
-    <mergeCell ref="AF5:AF35"/>
-    <mergeCell ref="Y5:Y35"/>
     <mergeCell ref="A2:AJ2"/>
     <mergeCell ref="A1:AJ1"/>
     <mergeCell ref="R5:R35"/>
@@ -8661,37 +8834,47 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM6:AN6"/>
+    <mergeCell ref="AF5:AF35"/>
+    <mergeCell ref="Y5:Y35"/>
   </mergeCells>
-  <conditionalFormatting sqref="F6:J35 L6:Q35 S6:X35 Z6:AE35 F4:AJ5 AG6:AJ35">
-    <cfRule type="expression" dxfId="6" priority="8">
+  <conditionalFormatting sqref="B5:B33">
+    <cfRule type="duplicateValues" dxfId="14" priority="293"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:AJ5 F6:J35 L6:Q35 S6:X35 Z6:AE35 AG6:AJ35">
+    <cfRule type="expression" dxfId="13" priority="10">
+      <formula>F$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:AJ5 F6:J35 L6:Q35 S6:X35 Z6:AE35 AG6:AJ35">
+    <cfRule type="expression" dxfId="12" priority="9">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:J35 L6:Q35 S6:X35 Z6:AE35 F5:AJ5 AG6:AJ35">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+  <conditionalFormatting sqref="F5:AJ5 F6:J35 L6:Q35 S6:X35 Z6:AE35 AG6:AJ35">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:J35 L6:Q35 S6:X35 Z6:AE35 F3:AJ5 AG6:AJ35">
-    <cfRule type="expression" dxfId="3" priority="9">
-      <formula>F$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AL3 AK5:AL35">
-    <cfRule type="expression" dxfId="2" priority="10">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM7:AN7 AM8:AM9 AM12:AM14 AN18:AP18 AM18:AM20">
-    <cfRule type="expression" dxfId="1" priority="73">
+    <cfRule type="expression" dxfId="8" priority="74">
       <formula>AM$6="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B33">
-    <cfRule type="duplicateValues" dxfId="0" priority="292"/>
+  <conditionalFormatting sqref="F5:AJ35">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
